--- a/runs/ceattle/BSP0.xlsx
+++ b/runs/ceattle/BSP0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBFADB2-CA04-EA43-9AF8-8667B5EBEDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E750070-AF8E-BE42-BD33-DBC59D17FBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="-21100" windowWidth="34560" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="284">
   <si>
     <t>Number</t>
   </si>
@@ -901,12 +901,15 @@
   <si>
     <t>ATS_1</t>
   </si>
+  <si>
+    <t>Age_max_selected_upper</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -921,6 +924,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -949,13 +958,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -26063,7 +26073,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
@@ -26078,9 +26088,10 @@
     <col min="20" max="20" width="15.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -26162,8 +26173,11 @@
       <c r="AA1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB1" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -26183,7 +26197,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -26240,10 +26254,13 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="AB2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>163</v>
       </c>
@@ -26320,7 +26337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>164</v>
       </c>
@@ -26397,7 +26414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>165</v>
       </c>
@@ -26474,7 +26491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>281</v>
       </c>
@@ -26512,7 +26529,7 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -26551,7 +26568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>282</v>
       </c>
@@ -26589,7 +26606,7 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -41440,7 +41457,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -41503,6 +41520,130 @@
       </c>
       <c r="T1" s="1" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/runs/ceattle/BSP0.xlsx
+++ b/runs/ceattle/BSP0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E750070-AF8E-BE42-BD33-DBC59D17FBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8652FDA9-C2DB-3447-A3A7-63D39EADC562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="-21100" windowWidth="34560" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26077,18 +26077,18 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.25">
@@ -26114,67 +26114,67 @@
         <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
@@ -26200,17 +26200,17 @@
         <v>9</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>0.7</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
       <c r="L2">
         <v>1</v>
       </c>
@@ -26230,34 +26230,34 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
       <c r="X2">
         <v>0</v>
       </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -26280,16 +26280,13 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -26304,37 +26301,40 @@
         <v>1</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
       <c r="X3">
         <v>0</v>
       </c>
-      <c r="Y3">
-        <v>1</v>
-      </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -26357,19 +26357,16 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -26381,37 +26378,40 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
       <c r="X4">
         <v>0</v>
       </c>
-      <c r="Y4">
-        <v>1</v>
-      </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -26434,19 +26434,16 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -26458,37 +26455,40 @@
         <v>1</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
       <c r="X5">
         <v>0</v>
       </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26511,61 +26511,61 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>2</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>4</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>5</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
       <c r="X6">
         <v>0</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
         <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -26588,61 +26588,61 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>2</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>4</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>6</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
       <c r="X7">
         <v>0</v>
       </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AA7">
         <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/runs/ceattle/BSP0.xlsx
+++ b/runs/ceattle/BSP0.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8652FDA9-C2DB-3447-A3A7-63D39EADC562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D320B21-5554-0F4E-A098-8CE26759EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="-21100" windowWidth="34560" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="34560" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="meta_data" sheetId="1" r:id="rId1"/>
-    <sheet name="control" sheetId="2" r:id="rId2"/>
-    <sheet name="fleet_control" sheetId="3" r:id="rId3"/>
-    <sheet name="index_data" sheetId="4" r:id="rId4"/>
-    <sheet name="catch_data" sheetId="5" r:id="rId5"/>
+    <sheet name="catch_data" sheetId="5" r:id="rId1"/>
+    <sheet name="meta_data" sheetId="1" r:id="rId2"/>
+    <sheet name="control" sheetId="2" r:id="rId3"/>
+    <sheet name="fleet_control" sheetId="3" r:id="rId4"/>
+    <sheet name="index_data" sheetId="4" r:id="rId5"/>
     <sheet name="comp_data" sheetId="6" r:id="rId6"/>
     <sheet name="emp_sel" sheetId="7" r:id="rId7"/>
     <sheet name="NByageFixed" sheetId="8" r:id="rId8"/>
@@ -1269,905 +1269,1620 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="169.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
-      </c>
-      <c r="G26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>19</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>20</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>118</v>
-      </c>
-      <c r="G29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>24</v>
-      </c>
-      <c r="C32" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>25</v>
-      </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>26</v>
-      </c>
-      <c r="B34" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" t="s">
-        <v>133</v>
-      </c>
-      <c r="F34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" t="s">
-        <v>136</v>
-      </c>
-      <c r="F35" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>28</v>
-      </c>
-      <c r="B36" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" t="s">
-        <v>138</v>
-      </c>
-      <c r="D36" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" t="s">
-        <v>140</v>
-      </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>31</v>
-      </c>
-      <c r="B39" t="s">
-        <v>128</v>
-      </c>
-      <c r="C39" t="s">
-        <v>144</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>32</v>
-      </c>
-      <c r="B40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>33</v>
-      </c>
-      <c r="B41" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>34</v>
-      </c>
-      <c r="B42" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
-        <v>128</v>
-      </c>
-      <c r="C43" t="s">
-        <v>149</v>
-      </c>
-      <c r="D43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>36</v>
-      </c>
-      <c r="B44" t="s">
-        <v>128</v>
-      </c>
-      <c r="C44" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>37</v>
-      </c>
-      <c r="C45" t="s">
-        <v>151</v>
-      </c>
-      <c r="D45" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>38</v>
-      </c>
-      <c r="C46" t="s">
-        <v>153</v>
-      </c>
-      <c r="D46" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>39</v>
-      </c>
-      <c r="C47" t="s">
-        <v>155</v>
-      </c>
-      <c r="D47" t="s">
-        <v>156</v>
+        <v>173</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1964</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>174.792</v>
+      </c>
+      <c r="H2">
+        <v>0.56384999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1965</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>230.55099999999999</v>
+      </c>
+      <c r="H3">
+        <v>0.38424999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1966</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>261.678</v>
+      </c>
+      <c r="H4">
+        <v>0.35361999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1967</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>550.36199999999997</v>
+      </c>
+      <c r="H5">
+        <v>0.67945999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1968</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>702.18100000000004</v>
+      </c>
+      <c r="H6">
+        <v>0.62695000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1969</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>862.78899999999999</v>
+      </c>
+      <c r="H7">
+        <v>0.60335000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1970</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1256.5650000000001</v>
+      </c>
+      <c r="H8">
+        <v>1.0384800000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1971</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1743.7629999999999</v>
+      </c>
+      <c r="H9">
+        <v>1.5569299999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1972</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1874.5340000000001</v>
+      </c>
+      <c r="H10">
+        <v>1.5365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1973</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1758.9190000000001</v>
+      </c>
+      <c r="H11">
+        <v>1.7244299999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1974</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1588.39</v>
+      </c>
+      <c r="H12">
+        <v>1.5726599999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1975</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1356.7360000000001</v>
+      </c>
+      <c r="H13">
+        <v>1.49092</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1976</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1177.8219999999999</v>
+      </c>
+      <c r="H14">
+        <v>1.28024</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1977</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>978.37</v>
+      </c>
+      <c r="H15">
+        <v>1.526946667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1978</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>979.43100000000004</v>
+      </c>
+      <c r="H16">
+        <v>1.5219494440000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1979</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>935.71400000000006</v>
+      </c>
+      <c r="H17">
+        <v>1.5195243519999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1980</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>958.28</v>
+      </c>
+      <c r="H18">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1981</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>973.50199999999995</v>
+      </c>
+      <c r="H19">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1982</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>955.96400000000006</v>
+      </c>
+      <c r="H20">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1983</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>981.45</v>
+      </c>
+      <c r="H21">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1984</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1092.0550000000001</v>
+      </c>
+      <c r="H22">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1985</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1139.6759999999999</v>
+      </c>
+      <c r="H23">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1986</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1141.9929999999999</v>
+      </c>
+      <c r="H24">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1987</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>859.41600000000005</v>
+      </c>
+      <c r="H25">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1988</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1228.721</v>
+      </c>
+      <c r="H26">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1989</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1229.5999999999999</v>
+      </c>
+      <c r="H27">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1990</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1455.193</v>
+      </c>
+      <c r="H28">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1991</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1195.6639299999999</v>
+      </c>
+      <c r="H29">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1992</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1390.30916</v>
+      </c>
+      <c r="H30">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1993</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1326.60896</v>
+      </c>
+      <c r="H31">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1994</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1329.3730599999999</v>
+      </c>
+      <c r="H32">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1995</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1264.2468899999999</v>
+      </c>
+      <c r="H33">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1996</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1192.7810899999999</v>
+      </c>
+      <c r="H34">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1997</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1124.4330500000001</v>
+      </c>
+      <c r="H35">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1998</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1102.15914</v>
+      </c>
+      <c r="H36">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1999</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>989.68030999999996</v>
+      </c>
+      <c r="H37">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>2000</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>1132.70985</v>
+      </c>
+      <c r="H38">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2001</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>1387.1970200000001</v>
+      </c>
+      <c r="H39">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>2002</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>1480.77611</v>
+      </c>
+      <c r="H40">
+        <v>1.48537341</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>2003</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>1490.779227</v>
+      </c>
+      <c r="H41">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>174</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>2004</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1480.5516689999999</v>
+      </c>
+      <c r="H42">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>2005</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>1483.0218090000001</v>
+      </c>
+      <c r="H43">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>2006</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1488.0310449999999</v>
+      </c>
+      <c r="H44">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>2007</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>1354.5017889999999</v>
+      </c>
+      <c r="H45">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>2008</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>990.57806800000003</v>
+      </c>
+      <c r="H46">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>2009</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>810.78434600000003</v>
+      </c>
+      <c r="H47">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>2010</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>810.1859078</v>
+      </c>
+      <c r="H48">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>2011</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>1199.0406250000001</v>
+      </c>
+      <c r="H49">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>2012</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1205.221865</v>
+      </c>
+      <c r="H50">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>2013</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>1270.7704679999999</v>
+      </c>
+      <c r="H51">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>2014</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>1297.422339</v>
+      </c>
+      <c r="H52">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>2015</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1321.583785</v>
+      </c>
+      <c r="H53">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>2016</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>1352.6807960000001</v>
+      </c>
+      <c r="H54">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>2017</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1359.182092</v>
+      </c>
+      <c r="H55">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2018</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>1379.2872689999999</v>
+      </c>
+      <c r="H56">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>2019</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1409.3371380000001</v>
+      </c>
+      <c r="H57">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>2020</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1367.2290399999999</v>
+      </c>
+      <c r="H58">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>2021</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>1376.257582</v>
+      </c>
+      <c r="H59">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>2022</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1105.418688</v>
+      </c>
+      <c r="H60">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>2023</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1310.7156</v>
+      </c>
+      <c r="H61">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>174</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>2024</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>1300</v>
+      </c>
+      <c r="H62">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -25916,6 +26631,913 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="169.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>37</v>
+      </c>
+      <c r="C45" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -26071,7 +27693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -26197,19 +27819,19 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -26650,7 +28272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -31154,1628 +32776,6 @@
       <c r="I153">
         <f t="shared" si="0"/>
         <v>2029.9268904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1964</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>174.792</v>
-      </c>
-      <c r="H2">
-        <v>0.56384999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1965</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>230.55099999999999</v>
-      </c>
-      <c r="H3">
-        <v>0.38424999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1966</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>261.678</v>
-      </c>
-      <c r="H4">
-        <v>0.35361999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1967</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>550.36199999999997</v>
-      </c>
-      <c r="H5">
-        <v>0.67945999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1968</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>702.18100000000004</v>
-      </c>
-      <c r="H6">
-        <v>0.62695000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1969</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>862.78899999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.60335000000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1970</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1256.5650000000001</v>
-      </c>
-      <c r="H8">
-        <v>1.0384800000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1971</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1743.7629999999999</v>
-      </c>
-      <c r="H9">
-        <v>1.5569299999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1972</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1874.5340000000001</v>
-      </c>
-      <c r="H10">
-        <v>1.5365</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1973</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1758.9190000000001</v>
-      </c>
-      <c r="H11">
-        <v>1.7244299999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1974</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1588.39</v>
-      </c>
-      <c r="H12">
-        <v>1.5726599999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1975</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>1356.7360000000001</v>
-      </c>
-      <c r="H13">
-        <v>1.49092</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>174</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1976</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1177.8219999999999</v>
-      </c>
-      <c r="H14">
-        <v>1.28024</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1977</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>978.37</v>
-      </c>
-      <c r="H15">
-        <v>1.526946667</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1978</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>979.43100000000004</v>
-      </c>
-      <c r="H16">
-        <v>1.5219494440000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>174</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1979</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>935.71400000000006</v>
-      </c>
-      <c r="H17">
-        <v>1.5195243519999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1980</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>958.28</v>
-      </c>
-      <c r="H18">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1981</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>973.50199999999995</v>
-      </c>
-      <c r="H19">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1982</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>955.96400000000006</v>
-      </c>
-      <c r="H20">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>174</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1983</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>981.45</v>
-      </c>
-      <c r="H21">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1984</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1092.0550000000001</v>
-      </c>
-      <c r="H22">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>174</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1985</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>1139.6759999999999</v>
-      </c>
-      <c r="H23">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1986</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1141.9929999999999</v>
-      </c>
-      <c r="H24">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1987</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>859.41600000000005</v>
-      </c>
-      <c r="H25">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>174</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1988</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1228.721</v>
-      </c>
-      <c r="H26">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1989</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>1229.5999999999999</v>
-      </c>
-      <c r="H27">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>1990</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>1455.193</v>
-      </c>
-      <c r="H28">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>174</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1991</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1195.6639299999999</v>
-      </c>
-      <c r="H29">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1992</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>1390.30916</v>
-      </c>
-      <c r="H30">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>174</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>1993</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>1326.60896</v>
-      </c>
-      <c r="H31">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>174</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1994</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32">
-        <v>1329.3730599999999</v>
-      </c>
-      <c r="H32">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>174</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1995</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>1264.2468899999999</v>
-      </c>
-      <c r="H33">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>174</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1996</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>1192.7810899999999</v>
-      </c>
-      <c r="H34">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>174</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1997</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35">
-        <v>1124.4330500000001</v>
-      </c>
-      <c r="H35">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>174</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1998</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>1102.15914</v>
-      </c>
-      <c r="H36">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>174</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1999</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37">
-        <v>989.68030999999996</v>
-      </c>
-      <c r="H37">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>2000</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38">
-        <v>1132.70985</v>
-      </c>
-      <c r="H38">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>174</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>2001</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39">
-        <v>1387.1970200000001</v>
-      </c>
-      <c r="H39">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>2002</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40">
-        <v>1480.77611</v>
-      </c>
-      <c r="H40">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>174</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>2003</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41">
-        <v>1490.779227</v>
-      </c>
-      <c r="H41">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>174</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>2004</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>1480.5516689999999</v>
-      </c>
-      <c r="H42">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>174</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>2005</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
-        <v>1483.0218090000001</v>
-      </c>
-      <c r="H43">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>2006</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>1488.0310449999999</v>
-      </c>
-      <c r="H44">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>174</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>2007</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45">
-        <v>1354.5017889999999</v>
-      </c>
-      <c r="H45">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>174</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>2008</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46">
-        <v>990.57806800000003</v>
-      </c>
-      <c r="H46">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>174</v>
-      </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>2009</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>810.78434600000003</v>
-      </c>
-      <c r="H47">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>2010</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48">
-        <v>810.1859078</v>
-      </c>
-      <c r="H48">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>2011</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
-        <v>1199.0406250000001</v>
-      </c>
-      <c r="H49">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>174</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>2012</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
-        <v>1205.221865</v>
-      </c>
-      <c r="H50">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>174</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>2013</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51">
-        <v>1270.7704679999999</v>
-      </c>
-      <c r="H51">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>174</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>2014</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52">
-        <v>1297.422339</v>
-      </c>
-      <c r="H52">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>174</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>2015</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53">
-        <v>1321.583785</v>
-      </c>
-      <c r="H53">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>174</v>
-      </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>2016</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54">
-        <v>1352.6807960000001</v>
-      </c>
-      <c r="H54">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>174</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>2017</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55">
-        <v>1359.182092</v>
-      </c>
-      <c r="H55">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
-        <v>2018</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>1379.2872689999999</v>
-      </c>
-      <c r="H56">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>174</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>2019</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57">
-        <v>1409.3371380000001</v>
-      </c>
-      <c r="H57">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>2020</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58">
-        <v>1367.2290399999999</v>
-      </c>
-      <c r="H58">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>2021</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59">
-        <v>1376.257582</v>
-      </c>
-      <c r="H59">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>2022</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-      <c r="G60">
-        <v>1105.418688</v>
-      </c>
-      <c r="H60">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>174</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>2023</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61">
-        <v>1310.7156</v>
-      </c>
-      <c r="H61">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>2024</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62">
-        <v>1300</v>
-      </c>
-      <c r="H62">
-        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/runs/ceattle/BSP0.xlsx
+++ b/runs/ceattle/BSP0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D320B21-5554-0F4E-A098-8CE26759EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659D4635-DC2A-F044-9005-711CB7AF6D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1000" windowWidth="34560" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="34560" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catch_data" sheetId="5" r:id="rId1"/>
@@ -28274,13 +28274,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -28308,8 +28308,11 @@
       <c r="I1" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K1" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>172</v>
       </c>
@@ -28338,7 +28341,7 @@
         <v>563.28748559999997</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>172</v>
       </c>
@@ -28367,7 +28370,7 @@
         <v>694.716095</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>172</v>
       </c>
@@ -28396,7 +28399,7 @@
         <v>760.43397809999999</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>172</v>
       </c>
@@ -28425,7 +28428,7 @@
         <v>1051.46092</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>172</v>
       </c>
@@ -28454,7 +28457,7 @@
         <v>1342.493684</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -28483,7 +28486,7 @@
         <v>1135.9619660000001</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>172</v>
       </c>
@@ -28512,7 +28515,7 @@
         <v>1051.466257</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -28541,7 +28544,7 @@
         <v>1145.3486969999999</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -28570,7 +28573,7 @@
         <v>957.58478979999995</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>172</v>
       </c>
@@ -28599,7 +28602,7 @@
         <v>948.19851759999995</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -28628,7 +28631,7 @@
         <v>854.31489190000002</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>172</v>
       </c>
@@ -28657,7 +28660,7 @@
         <v>863.70461160000002</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>163</v>
       </c>
@@ -28686,7 +28689,7 @@
         <v>407.97433100000006</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>163</v>
       </c>
@@ -28715,7 +28718,7 @@
         <v>795.43823999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>163</v>
       </c>

--- a/runs/ceattle/BSP0.xlsx
+++ b/runs/ceattle/BSP0.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659D4635-DC2A-F044-9005-711CB7AF6D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DC6EEF-D6A9-FA4B-8B1D-A278C60D86DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1000" windowWidth="34560" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="catch_data" sheetId="5" r:id="rId1"/>
-    <sheet name="meta_data" sheetId="1" r:id="rId2"/>
-    <sheet name="control" sheetId="2" r:id="rId3"/>
-    <sheet name="fleet_control" sheetId="3" r:id="rId4"/>
+    <sheet name="meta_data" sheetId="1" r:id="rId1"/>
+    <sheet name="control" sheetId="2" r:id="rId2"/>
+    <sheet name="fleet_control" sheetId="3" r:id="rId3"/>
+    <sheet name="catch_data" sheetId="5" r:id="rId4"/>
     <sheet name="index_data" sheetId="4" r:id="rId5"/>
     <sheet name="comp_data" sheetId="6" r:id="rId6"/>
     <sheet name="emp_sel" sheetId="7" r:id="rId7"/>
@@ -958,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -966,6 +966,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1269,1620 +1272,905 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="169.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1964</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>174.792</v>
-      </c>
-      <c r="H2">
-        <v>0.56384999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1965</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>230.55099999999999</v>
-      </c>
-      <c r="H3">
-        <v>0.38424999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1966</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>261.678</v>
-      </c>
-      <c r="H4">
-        <v>0.35361999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1967</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>550.36199999999997</v>
-      </c>
-      <c r="H5">
-        <v>0.67945999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1968</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>702.18100000000004</v>
-      </c>
-      <c r="H6">
-        <v>0.62695000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1969</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>862.78899999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.60335000000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1970</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1256.5650000000001</v>
-      </c>
-      <c r="H8">
-        <v>1.0384800000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1971</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1743.7629999999999</v>
-      </c>
-      <c r="H9">
-        <v>1.5569299999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1972</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1874.5340000000001</v>
-      </c>
-      <c r="H10">
-        <v>1.5365</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1973</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1758.9190000000001</v>
-      </c>
-      <c r="H11">
-        <v>1.7244299999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1974</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1588.39</v>
-      </c>
-      <c r="H12">
-        <v>1.5726599999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1975</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>1356.7360000000001</v>
-      </c>
-      <c r="H13">
-        <v>1.49092</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>174</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1976</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1177.8219999999999</v>
-      </c>
-      <c r="H14">
-        <v>1.28024</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1977</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>978.37</v>
-      </c>
-      <c r="H15">
-        <v>1.526946667</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1978</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>979.43100000000004</v>
-      </c>
-      <c r="H16">
-        <v>1.5219494440000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>174</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1979</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>935.71400000000006</v>
-      </c>
-      <c r="H17">
-        <v>1.5195243519999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1980</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>958.28</v>
-      </c>
-      <c r="H18">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1981</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>973.50199999999995</v>
-      </c>
-      <c r="H19">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1982</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>955.96400000000006</v>
-      </c>
-      <c r="H20">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>174</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1983</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>981.45</v>
-      </c>
-      <c r="H21">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1984</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1092.0550000000001</v>
-      </c>
-      <c r="H22">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>174</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1985</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>1139.6759999999999</v>
-      </c>
-      <c r="H23">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1986</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1141.9929999999999</v>
-      </c>
-      <c r="H24">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1987</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>859.41600000000005</v>
-      </c>
-      <c r="H25">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>174</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1988</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1228.721</v>
-      </c>
-      <c r="H26">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1989</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>1229.5999999999999</v>
-      </c>
-      <c r="H27">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>1990</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>1455.193</v>
-      </c>
-      <c r="H28">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>174</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1991</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1195.6639299999999</v>
-      </c>
-      <c r="H29">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1992</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>1390.30916</v>
-      </c>
-      <c r="H30">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>174</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>1993</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>1326.60896</v>
-      </c>
-      <c r="H31">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>174</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1994</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32">
-        <v>1329.3730599999999</v>
-      </c>
-      <c r="H32">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>174</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1995</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>1264.2468899999999</v>
-      </c>
-      <c r="H33">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>174</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1996</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>1192.7810899999999</v>
-      </c>
-      <c r="H34">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>174</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1997</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35">
-        <v>1124.4330500000001</v>
-      </c>
-      <c r="H35">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>174</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1998</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>1102.15914</v>
-      </c>
-      <c r="H36">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>174</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1999</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37">
-        <v>989.68030999999996</v>
-      </c>
-      <c r="H37">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>2000</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38">
-        <v>1132.70985</v>
-      </c>
-      <c r="H38">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>174</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>2001</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39">
-        <v>1387.1970200000001</v>
-      </c>
-      <c r="H39">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>2002</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40">
-        <v>1480.77611</v>
-      </c>
-      <c r="H40">
-        <v>1.48537341</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>174</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>2003</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41">
-        <v>1490.779227</v>
-      </c>
-      <c r="H41">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>174</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>2004</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>1480.5516689999999</v>
-      </c>
-      <c r="H42">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>174</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>2005</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
-        <v>1483.0218090000001</v>
-      </c>
-      <c r="H43">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>2006</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>1488.0310449999999</v>
-      </c>
-      <c r="H44">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>174</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>2007</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45">
-        <v>1354.5017889999999</v>
-      </c>
-      <c r="H45">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>174</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>2008</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46">
-        <v>990.57806800000003</v>
-      </c>
-      <c r="H46">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>174</v>
-      </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>2009</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>810.78434600000003</v>
-      </c>
-      <c r="H47">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>2010</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48">
-        <v>810.1859078</v>
-      </c>
-      <c r="H48">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>2011</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
-        <v>1199.0406250000001</v>
-      </c>
-      <c r="H49">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>174</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>2012</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
-        <v>1205.221865</v>
-      </c>
-      <c r="H50">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>174</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>2013</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51">
-        <v>1270.7704679999999</v>
-      </c>
-      <c r="H51">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>174</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>2014</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52">
-        <v>1297.422339</v>
-      </c>
-      <c r="H52">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>174</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>2015</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53">
-        <v>1321.583785</v>
-      </c>
-      <c r="H53">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>174</v>
-      </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>2016</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54">
-        <v>1352.6807960000001</v>
-      </c>
-      <c r="H54">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>174</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>2017</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55">
-        <v>1359.182092</v>
-      </c>
-      <c r="H55">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
-        <v>2018</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>1379.2872689999999</v>
-      </c>
-      <c r="H56">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>174</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>2019</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57">
-        <v>1409.3371380000001</v>
-      </c>
-      <c r="H57">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>2020</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58">
-        <v>1367.2290399999999</v>
-      </c>
-      <c r="H58">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>2021</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59">
-        <v>1376.257582</v>
-      </c>
-      <c r="H59">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>2022</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-      <c r="G60">
-        <v>1105.418688</v>
-      </c>
-      <c r="H60">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>174</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>2023</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61">
-        <v>1310.7156</v>
-      </c>
-      <c r="H61">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>2024</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62">
-        <v>1300</v>
-      </c>
-      <c r="H62">
-        <v>1.4</v>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>37</v>
+      </c>
+      <c r="C45" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -26631,913 +25919,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="169.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
-      </c>
-      <c r="G26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>19</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>20</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>118</v>
-      </c>
-      <c r="G29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>24</v>
-      </c>
-      <c r="C32" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>25</v>
-      </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>26</v>
-      </c>
-      <c r="B34" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" t="s">
-        <v>133</v>
-      </c>
-      <c r="F34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" t="s">
-        <v>136</v>
-      </c>
-      <c r="F35" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>28</v>
-      </c>
-      <c r="B36" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" t="s">
-        <v>138</v>
-      </c>
-      <c r="D36" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" t="s">
-        <v>140</v>
-      </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>31</v>
-      </c>
-      <c r="B39" t="s">
-        <v>128</v>
-      </c>
-      <c r="C39" t="s">
-        <v>144</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>32</v>
-      </c>
-      <c r="B40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>33</v>
-      </c>
-      <c r="B41" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>34</v>
-      </c>
-      <c r="B42" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
-        <v>128</v>
-      </c>
-      <c r="C43" t="s">
-        <v>149</v>
-      </c>
-      <c r="D43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>36</v>
-      </c>
-      <c r="B44" t="s">
-        <v>128</v>
-      </c>
-      <c r="C44" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>37</v>
-      </c>
-      <c r="C45" t="s">
-        <v>151</v>
-      </c>
-      <c r="D45" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>38</v>
-      </c>
-      <c r="C46" t="s">
-        <v>153</v>
-      </c>
-      <c r="D46" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>39</v>
-      </c>
-      <c r="C47" t="s">
-        <v>155</v>
-      </c>
-      <c r="D47" t="s">
-        <v>156</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -27693,7 +26074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -28272,6 +26653,1690 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1964</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>174.792</v>
+      </c>
+      <c r="H2">
+        <f>LOG(0.05*G2)</f>
+        <v>0.94149155600189527</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1965</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>230.55099999999999</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H62" si="0">LOG(0.05*G3)</f>
+        <v>1.0617370146196605</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1966</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>261.678</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>1.1167372161611253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1967</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>550.36199999999997</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>1.4396184445343414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1968</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>702.18100000000004</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>1.5454190782451958</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1969</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>862.78899999999999</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>1.6348746038289346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1970</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1256.5650000000001</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>1.7981549631708516</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1971</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1743.7629999999999</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>1.9404574626925988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1972</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1874.5340000000001</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>1.9718633263293697</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1973</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1758.9190000000001</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>1.9442158445535656</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1974</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1588.39</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>1.8999271485560625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1975</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1356.7360000000001</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>1.8314653531767227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1976</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1177.8219999999999</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>1.770049666384</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1977</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>978.37</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>1.6894731316898732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1978</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>979.43100000000004</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>1.6899438501034498</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1979</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>935.71400000000006</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>1.6701131317045228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1980</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>958.28</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>1.6804624285374037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1981</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>973.50199999999995</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>1.6873068524242949</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1982</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>955.96400000000006</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>1.6794115421186762</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1983</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>981.45</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>1.6908381836900628</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1984</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1092.0550000000001</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>1.7372145159602275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1985</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1139.6759999999999</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>1.7557514070656859</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1986</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1141.9929999999999</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>1.75663344618745</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1987</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>859.41600000000005</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>1.6331734391470485</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1988</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1228.721</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>1.788423285175315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1989</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1229.5999999999999</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>1.7887338588277075</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1990</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1455.193</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>1.861890601284323</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1991</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1195.6639299999999</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>1.7765791322689672</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1992</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1390.30916</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>1.842081388440939</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1993</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1326.60896</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="0"/>
+        <v>1.8217129305604123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1994</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1329.3730599999999</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="0"/>
+        <v>1.822616877802355</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1995</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1264.2468899999999</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>1.800801898293755</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1996</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1192.7810899999999</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>1.775530749658764</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1997</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1124.4330500000001</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>1.7499036064988165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1998</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1102.15914</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>1.7412143108608373</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1999</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>989.68030999999996</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>1.6944649342621214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>2000</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>1132.70985</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="0"/>
+        <v>1.7530886814706419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2001</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>1387.1970200000001</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="0"/>
+        <v>1.8411081515104362</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>2002</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>1480.77611</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="0"/>
+        <v>1.8694594034770937</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>2003</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>1490.779227</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="0"/>
+        <v>1.8723833368601825</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>174</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>2004</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1480.5516689999999</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="0"/>
+        <v>1.8693935725422741</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>2005</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>1483.0218090000001</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="0"/>
+        <v>1.8701175420526763</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>2006</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1488.0310449999999</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="0"/>
+        <v>1.8715819963869702</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>2007</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>1354.5017889999999</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="0"/>
+        <v>1.8307495873134119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>2008</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>990.57806800000003</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="0"/>
+        <v>1.6948587125453267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>2009</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>810.78434600000003</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="0"/>
+        <v>1.6078753594144037</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>2010</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>810.1859078</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="0"/>
+        <v>1.6075546892241659</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>2011</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>1199.0406250000001</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="0"/>
+        <v>1.7778039021258074</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>2012</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1205.221865</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="0"/>
+        <v>1.7800370063306257</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>2013</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>1270.7704679999999</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>1.8030371178458122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>2014</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>1297.422339</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="0"/>
+        <v>1.8120513756710228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>2015</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1321.5837850000003</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>1.8200647058254729</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>2016</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>1352.6807960000001</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
+        <v>1.8301653287302322</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>2017</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1359.182092</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>1.8322476481569718</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2018</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>1379.2872689999999</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>1.8386247319684217</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>2019</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1409.3371380000001</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>1.8479849006809139</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>2020</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1367.2290399999999</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="0"/>
+        <v>1.834811278578991</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>2021</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>1376.257582</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="0"/>
+        <v>1.8376697289128781</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>2022</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1105.418688</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="0"/>
+        <v>1.742496806744497</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>2023</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1310.7156</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="0"/>
+        <v>1.8164784727235161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>174</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>2024</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>1300</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="0"/>
+        <v>1.8129133566428555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K153"/>

--- a/runs/ceattle/BSP0.xlsx
+++ b/runs/ceattle/BSP0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DC6EEF-D6A9-FA4B-8B1D-A278C60D86DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCA55CF-E71D-A240-8DD9-0CECFD4947BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1000" windowWidth="34560" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="34560" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>
@@ -26200,13 +26200,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>0</v>
